--- a/artfynd/A 26326-2024 artfynd.xlsx
+++ b/artfynd/A 26326-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110398662</v>
+        <v>113178103</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ammerberget, Jmt</t>
+          <t>Hällmyrorna, sydost om, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542740.0786278071</v>
+        <v>542974</v>
       </c>
       <c r="R2" t="n">
-        <v>7018219.26298263</v>
+        <v>7018255</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,31 +756,43 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>äldre barrblandskog på frisk mark med blåbär</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>2 substratenheter # barkfallna äldre tallågor</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Louise Almén</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Louise Almén</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110398669</v>
+        <v>113178102</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,34 +800,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ammerberget, Jmt</t>
+          <t>Hällmyrorna, sydost om, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542972.8129257357</v>
+        <v>542953</v>
       </c>
       <c r="R3" t="n">
-        <v>7018234.062416743</v>
+        <v>7018263</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,22 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,70 +870,78 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>äldre barrblandskog på frisk mark med blåbär</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # vitrötad splint på 70 cm grov gammal skortenshögstubbe</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Louise Almén</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Louise Almén</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110398663</v>
+        <v>110398669</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ammerberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542760.2179950954</v>
+        <v>542973</v>
       </c>
       <c r="R4" t="n">
-        <v>7018229.429174601</v>
+        <v>7018234</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +971,9 @@
           <t>2023-06-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,15 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110398666</v>
+        <v>110398662</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542793.829217178</v>
+        <v>542740</v>
       </c>
       <c r="R5" t="n">
-        <v>7018242.924195541</v>
+        <v>7018219</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1072,9 @@
           <t>2023-06-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,50 +1101,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110398664</v>
+        <v>110398663</v>
       </c>
       <c r="B6" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229748</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ammerberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542780.0264464815</v>
+        <v>542760</v>
       </c>
       <c r="R6" t="n">
-        <v>7018230.592454774</v>
+        <v>7018230</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,19 +1173,9 @@
           <t>2023-06-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,15 +1202,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110398668</v>
+        <v>110398665</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,7 +1232,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1291,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542927.6344756588</v>
+        <v>542780</v>
       </c>
       <c r="R7" t="n">
-        <v>7018243.357563224</v>
+        <v>7018231</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,19 +1274,9 @@
           <t>2023-06-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,15 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110398665</v>
+        <v>110398666</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,7 +1333,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1407,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542780.0264464815</v>
+        <v>542794</v>
       </c>
       <c r="R8" t="n">
-        <v>7018230.592454774</v>
+        <v>7018243</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,19 +1375,9 @@
           <t>2023-06-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,50 +1404,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113178101</v>
+        <v>110398667</v>
       </c>
       <c r="B9" t="n">
-        <v>78247</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hällmyrorna, sydost om, Jmt</t>
+          <t>Ammerberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542845</v>
+        <v>542831</v>
       </c>
       <c r="R9" t="n">
-        <v>7018263</v>
+        <v>7018235</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,12 +1473,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,83 +1489,65 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>äldre tallblandskog med björk på frisk mark med blåbär</t>
-        </is>
-      </c>
-      <c r="AN9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>1 substratenheter # 60 cm grov, kolad gammal skortenshögstubbe</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113178103</v>
+        <v>110398668</v>
       </c>
       <c r="B10" t="n">
-        <v>95203</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hällmyrorna, sydost om, Jmt</t>
+          <t>Ammerberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>542974</v>
+        <v>542928</v>
       </c>
       <c r="R10" t="n">
-        <v>7018255</v>
+        <v>7018244</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,12 +1574,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,48 +1590,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>äldre barrblandskog på frisk mark med blåbär</t>
-        </is>
-      </c>
-      <c r="AN10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>2 substratenheter # barkfallna äldre tallågor</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113178102</v>
+        <v>113178101</v>
       </c>
       <c r="B11" t="n">
-        <v>80429</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,21 +1617,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1757,7 +1641,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>542953</v>
+        <v>542845</v>
       </c>
       <c r="R11" t="n">
         <v>7018263</v>
@@ -1806,7 +1690,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>äldre barrblandskog på frisk mark med blåbär</t>
+          <t>äldre tallblandskog med björk på frisk mark med blåbär</t>
         </is>
       </c>
       <c r="AN11" t="n">
@@ -1814,7 +1698,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>1 substratenheter # vitrötad splint på 70 cm grov gammal skortenshögstubbe</t>
+          <t>1 substratenheter # 60 cm grov, kolad gammal skortenshögstubbe</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1833,6 +1717,103 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>110398664</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ammerberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>542780</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7018231</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26326-2024 artfynd.xlsx
+++ b/artfynd/A 26326-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178103</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178102</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398669</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398662</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398663</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,6 +1330,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398665</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398666</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1502,6 +1542,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398667</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1603,6 +1648,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398668</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1717,6 +1767,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178101</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1814,8 +1869,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398664</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>